--- a/submission/EPSG_submission_Mozambique_LAEA.xlsx
+++ b/submission/EPSG_submission_Mozambique_LAEA.xlsx
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B8" s="141" t="inlineStr">
         <is>
-          <t>WGS 84 / Mozambique LAEA</t>
+          <t>WGS 84 / LAEA Mozambique</t>
         </is>
       </c>
       <c r="C8" s="138" t="n"/>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B9" s="141" t="inlineStr">
         <is>
-          <t>Mozambique Lambert Azimuthal Equal Area, Mozambique LAEA</t>
+          <t>Mozambique Lambert Azimuthal Equal Area</t>
         </is>
       </c>
       <c r="C9" s="138" t="n"/>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B27" s="151" t="inlineStr">
         <is>
-          <t>Mozambique LAEA</t>
+          <t>Mozambique Lambert Azimuthal Equal Area</t>
         </is>
       </c>
       <c r="C27" s="138" t="n"/>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B51" s="150" t="inlineStr">
         <is>
-          <t>Equal-area statistical analysis and national mapping of hydrological and remote-sensing products.</t>
+          <t>Statistical analysis.</t>
         </is>
       </c>
       <c r="C51" s="138" t="n"/>

--- a/submission/EPSG_submission_Mozambique_LAEA.xlsx
+++ b/submission/EPSG_submission_Mozambique_LAEA.xlsx
@@ -4600,11 +4600,7 @@
           <t>Alias</t>
         </is>
       </c>
-      <c r="B9" s="141" t="inlineStr">
-        <is>
-          <t>Mozambique Lambert Azimuthal Equal Area</t>
-        </is>
-      </c>
+      <c r="B9" s="141" t="n"/>
       <c r="C9" s="138" t="n"/>
       <c r="D9" s="138" t="n"/>
       <c r="E9" s="139" t="n"/>
@@ -6115,7 +6111,7 @@
       </c>
       <c r="B64" s="141" t="inlineStr">
         <is>
-          <t>LNEG technical note 'Definition of the projected CRS WGS 84 / Mozambique LAEA', Zenodo DOI: 10.5281/zenodo.21512485. Produced under DNGRH contract DNGRH-346682-CS-QCBS (World Bank financed), Mozambique hydrogeological mapping programme.</t>
+          <t>Goncalves, P. (2026). Definition of the projected coordinate reference system WGS 84 / LAEA Mozambique. LNEG technical note, version 1.0. https://doi.org/10.5281/zenodo.21512485</t>
         </is>
       </c>
       <c r="C64" s="138" t="n"/>
@@ -6152,7 +6148,7 @@
       </c>
       <c r="B65" s="181" t="inlineStr">
         <is>
-          <t>In production use in the LNEG hydro-rs processing system for national multitemporal Sentinel-1, Sentinel-2 and Landsat mosaics and derived hydrological products (water classification, groundwater potential and recharge zonation, GRACE water-storage grids) of the Mozambique hydrogeological mapping programme, led by the Direccao Nacional de Gestao de Recursos Hidricos (DNGRH) and World Bank financed; LNEG executes the remote-sensing component under contract DNGRH-346682-CS-QCBS. Products embed the full WKT2 definition. Base CRS is the WGS 84 ensemble because source data are natively WGS 84/ITRF and the scope is statistical and thematic, not cadastral (precedent: EASE-Grid 2.0, EPSG:6931-6933). The metric national alternatives, Moznet / UTM 36S and 37S (EPSG:3036, 3037), are conformal and split the country across two zones. Earlier working name 'Mozambique Lambert Azimuthal Equal Area (LNEG)' appears in products generated before registration and is retained as an alias; parameters are identical.</t>
+          <t>Used for equal-area statistical analysis of national remote-sensing and hydrological products. Replaces use of continental equal-area projections over Mozambique. In production use under DNGRH contract DNGRH-346682-CS-QCBS (World Bank programme P180171). Earlier products embed the label 'Mozambique Lambert Azimuthal Equal Area (LNEG)'.</t>
         </is>
       </c>
       <c r="C65" s="182" t="n"/>
